--- a/hasil_gabungan_vertikal_panjang_jalur.xlsx
+++ b/hasil_gabungan_vertikal_panjang_jalur.xlsx
@@ -1,15 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771B712E-6C9C-42DD-8D38-EC51BE5CD0BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -49,8 +66,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -60,6 +77,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -99,27 +123,39 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -157,7 +193,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -191,6 +227,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -225,9 +262,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -400,11 +438,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -418,7 +461,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -426,97 +469,109 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>25.31370849898476</v>
+        <v>24.142135623730951</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C3">
-        <v>52.04163056034262</v>
+        <v>23.963990038857649</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" s="3" t="e">
+        <f>(#REF!-C3)/#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C4">
-        <v>105.4974746830583</v>
+        <v>49.698484809835001</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C5">
-        <v>212.4091629284898</v>
+        <v>48.971601968780703</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="3" t="e">
+        <f>(C1-C5)/C1</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C6">
-        <v>27.55634918610405</v>
+        <v>100.8111831820431</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C7">
-        <v>55.32963226464916</v>
+        <v>99.109206619708829</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="3">
+        <f>(C3-C7)/C3</f>
+        <v>-3.1357556257953325</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C8">
-        <v>110.934942379664</v>
+        <v>203.0365799264593</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -524,13 +579,17 @@
         <v>128</v>
       </c>
       <c r="C9">
-        <v>222.1702210976759</v>
+        <v>199.42457255008571</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="3">
+        <f>(C5-C9)/C5</f>
+        <v>-3.0722493145561884</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -543,92 +602,120 @@
       <c r="D10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="3">
+        <f>(C6-C10)/C6</f>
+        <v>0.74649291497794601</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C11">
-        <v>51.69848480983499</v>
+        <v>26.055199887160551</v>
       </c>
       <c r="D11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" s="3">
+        <f>(C7-C11)/C7</f>
+        <v>0.73710616020631903</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
       <c r="B12">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C12">
-        <v>103.9827560572969</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="D12" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="3">
+        <f>(C8-C12)/C8</f>
+        <v>0.74537354387785493</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C13">
-        <v>208.5512985522207</v>
+        <v>52.28288660312667</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="3">
+        <f>(C9-C13)/C9</f>
+        <v>0.7378312715701284</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C14">
-        <v>26.05519988716055</v>
+        <v>103.9827560572969</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="3">
+        <f>(C10-C14)/C10</f>
+        <v>-3.068764098505754</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>5</v>
       </c>
       <c r="B15">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C15">
-        <v>52.28288660312667</v>
+        <v>105.108348609036</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="3">
+        <f>(C11-C15)/C11</f>
+        <v>-3.0340641815928326</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C16">
-        <v>105.108348609036</v>
+        <v>208.55129855222069</v>
       </c>
       <c r="D16" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="3">
+        <f>(C12-C16)/C12</f>
+        <v>-3.0339924723005893</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -636,13 +723,17 @@
         <v>128</v>
       </c>
       <c r="C17">
-        <v>211.0430492799173</v>
+        <v>211.04304927991731</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" s="3">
+        <f>(C13-C17)/C13</f>
+        <v>-3.0365607752670698</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -650,97 +741,125 @@
         <v>16</v>
       </c>
       <c r="C18">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="3">
+        <f>(C14-C18)/C14</f>
+        <v>0.75655859241664725</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C19">
-        <v>52.04163056034262</v>
+        <v>26.54977647648456</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="3">
+        <f>(C15-C19)/C15</f>
+        <v>0.74740563591918019</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
       <c r="B20">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C20">
-        <v>105.4974746830583</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20" s="3">
+        <f>(C16-C20)/C16</f>
+        <v>0.75046124899907285</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B21">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C21">
-        <v>212.4091629284898</v>
+        <v>53.498586721382473</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21" s="3">
+        <f>(C17-C21)/C17</f>
+        <v>0.74650391517787185</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C22">
-        <v>26.54977647648456</v>
+        <v>105.4974746830583</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22" s="3">
+        <f>(C18-C22)/C18</f>
+        <v>-3.1676024944069106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>5</v>
       </c>
       <c r="B23">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C23">
-        <v>53.49858672138247</v>
+        <v>106.8493377268543</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23" s="3">
+        <f>(C19-C23)/C19</f>
+        <v>-3.0244910469017312</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C24">
-        <v>106.8493377268543</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24" s="3">
+        <f>(C20-C24)/C20</f>
+        <v>-3.0815239768900007</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -748,13 +867,17 @@
         <v>128</v>
       </c>
       <c r="C25">
-        <v>214.3364735781256</v>
+        <v>214.33647357812561</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25" s="3">
+        <f>(C21-C25)/C21</f>
+        <v>-3.0063950603850058</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -767,92 +890,120 @@
       <c r="D26" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26" s="3">
+        <f>(C22-C26)/C22</f>
+        <v>0.77671172455195325</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B27">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C27">
-        <v>48.52691193458118</v>
+        <v>23.08709566447531</v>
       </c>
       <c r="D27" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27" s="3">
+        <f>(C23-C27)/C23</f>
+        <v>0.78392850947289616</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
       <c r="B28">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C28">
-        <v>98.46803743153546</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="D28" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28" s="3">
+        <f>(C24-C28)/C24</f>
+        <v>0.77154040218632947</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B29">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C29">
-        <v>198.350288425444</v>
+        <v>47.142608793074928</v>
       </c>
       <c r="D29" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29" s="3">
+        <f>(C25-C29)/C25</f>
+        <v>0.78005325922332358</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B30">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C30">
-        <v>23.08709566447531</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="D30" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30" s="3">
+        <f>(C26-C30)/C26</f>
+        <v>-3.1801060365339633</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
       <c r="B31">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C31">
-        <v>47.14260879307493</v>
+        <v>95.643929748144473</v>
       </c>
       <c r="D31" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31" s="3">
+        <f>(C27-C31)/C27</f>
+        <v>-3.1427441172392321</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B32">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C32">
-        <v>95.64392974814447</v>
+        <v>198.35028842544401</v>
       </c>
       <c r="D32" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32" s="3">
+        <f>(C28-C32)/C28</f>
+        <v>-3.0874286147208121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -860,13 +1011,17 @@
         <v>128</v>
       </c>
       <c r="C33">
-        <v>199.1787701724513</v>
+        <v>199.17877017245129</v>
       </c>
       <c r="D33" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33" s="3">
+        <f>(C29-C33)/C29</f>
+        <v>-3.2250264733272447</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -874,97 +1029,125 @@
         <v>16</v>
       </c>
       <c r="C34">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="E34" s="3">
+        <f>(C30-C34)/C30</f>
+        <v>0.76672061972953909</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B35">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C35">
-        <v>47.35533905932738</v>
+        <v>23.9102632953472</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="E35" s="3">
+        <f>(C31-C35)/C31</f>
+        <v>0.75000751894752571</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>4</v>
       </c>
       <c r="B36">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C36">
-        <v>96.12489168102785</v>
+        <v>47.355339059327378</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="E36" s="3">
+        <f>(C32-C36)/C32</f>
+        <v>0.76125399445976949</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B37">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C37">
-        <v>193.6639969244288</v>
+        <v>47.714742845122878</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37" s="3">
+        <f>(C33-C37)/C33</f>
+        <v>0.76044262747575508</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B38">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C38">
-        <v>23.9102632953472</v>
+        <v>96.124891681027847</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="E38" s="3">
+        <f>(C34-C38)/C34</f>
+        <v>-3.1846990312590648</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>5</v>
       </c>
       <c r="B39">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C39">
-        <v>47.71474284512288</v>
+        <v>95.528411805246748</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="E39" s="3">
+        <f>(C35-C39)/C35</f>
+        <v>-2.9952889947404318</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B40">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C40">
-        <v>95.52841180524675</v>
+        <v>193.6639969244288</v>
       </c>
       <c r="D40" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="41" spans="1:4">
+      <c r="E40" s="3">
+        <f>(C36-C40)/C36</f>
+        <v>-3.0895916019480731</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -977,8 +1160,16 @@
       <c r="D41" t="s">
         <v>9</v>
       </c>
+      <c r="E41" s="3">
+        <f>(C37-C41)/C37</f>
+        <v>-3.0304267665272637</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E41">
+    <sortCondition ref="D2:D41"/>
+    <sortCondition ref="B2:B41"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>